--- a/dataset_t6_grouped/results2/G4/G4_T6321_W0022F0003T0006Z000C1N46_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T6321_W0022F0003T0006Z000C1N46_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>43.23612652250061</v>
+        <v>7.02587055990635</v>
       </c>
       <c r="D2" t="n">
-        <v>17.35322554906782</v>
+        <v>2.819899151723521</v>
       </c>
       <c r="E2" t="n">
-        <v>10.0319950871124</v>
+        <v>1.630199201655766</v>
       </c>
       <c r="F2" t="n">
-        <v>5.583546579415767</v>
+        <v>0.9073263191550621</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>30.62916295167205</v>
+        <v>4.977238979646708</v>
       </c>
       <c r="D3" t="n">
-        <v>30.58209721628277</v>
+        <v>4.969590797645949</v>
       </c>
       <c r="E3" t="n">
-        <v>10.0319950871124</v>
+        <v>1.630199201655766</v>
       </c>
       <c r="F3" t="n">
-        <v>5.583546579415767</v>
+        <v>0.9073263191550621</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>37.66789939376892</v>
+        <v>6.121033651487449</v>
       </c>
       <c r="D4" t="n">
-        <v>36.54486649091118</v>
+        <v>5.938540804773067</v>
       </c>
       <c r="E4" t="n">
-        <v>10.0319950871124</v>
+        <v>1.630199201655766</v>
       </c>
       <c r="F4" t="n">
-        <v>5.583546579415767</v>
+        <v>0.9073263191550621</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>7.22292748292623</v>
+        <v>1.173725715975512</v>
       </c>
       <c r="D5" t="n">
-        <v>27.05894085877369</v>
+        <v>4.397077889550725</v>
       </c>
       <c r="E5" t="n">
-        <v>10.0319950871124</v>
+        <v>1.630199201655766</v>
       </c>
       <c r="F5" t="n">
-        <v>5.583546579415767</v>
+        <v>0.9073263191550621</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>25.5123306414162</v>
+        <v>4.145753729230133</v>
       </c>
       <c r="D6" t="n">
-        <v>21.82610554957155</v>
+        <v>3.546742151805377</v>
       </c>
       <c r="E6" t="n">
-        <v>10.0319950871124</v>
+        <v>1.630199201655766</v>
       </c>
       <c r="F6" t="n">
-        <v>5.583546579415767</v>
+        <v>0.9073263191550621</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>28.77693015475733</v>
+        <v>4.676251150148066</v>
       </c>
       <c r="D7" t="n">
-        <v>26.22547692804132</v>
+        <v>4.261640000806715</v>
       </c>
       <c r="E7" t="n">
-        <v>10.0319950871124</v>
+        <v>1.630199201655766</v>
       </c>
       <c r="F7" t="n">
-        <v>5.583546579415767</v>
+        <v>0.9073263191550621</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>30.75448678372623</v>
+        <v>4.997604102355513</v>
       </c>
       <c r="D8" t="n">
-        <v>32.10620873246155</v>
+        <v>5.217258919025001</v>
       </c>
       <c r="E8" t="n">
-        <v>10.0319950871124</v>
+        <v>1.630199201655766</v>
       </c>
       <c r="F8" t="n">
-        <v>5.583546579415767</v>
+        <v>0.9073263191550621</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>22.76877143228132</v>
+        <v>3.699925357745714</v>
       </c>
       <c r="D9" t="n">
-        <v>27.46032617442763</v>
+        <v>4.46230300334449</v>
       </c>
       <c r="E9" t="n">
-        <v>10.0319950871124</v>
+        <v>1.630199201655766</v>
       </c>
       <c r="F9" t="n">
-        <v>5.583546579415767</v>
+        <v>0.9073263191550621</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
